--- a/tests/sample_data/t1nc-20260129_ALL_ICCAT.xlsx
+++ b/tests/sample_data/t1nc-20260129_ALL_ICCAT.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -369,6 +369,11 @@
           <t>T1NC (1950-2024) [catches &gt;= 0, Catch type codes : FA, C, L, DD, DM, LF]</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -382,39 +387,261 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Time series start</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>1950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Time series start</t>
+          <t>Time series end</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Time series end</t>
+          <t>Total years</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Number of records</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>109703</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Number of species</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Number of fleets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Number of flags</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Number of parties</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Number of stocks</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Number of sample areas</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Number of areas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Number of catch types</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total catches</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>41597142.25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total estimated catches</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3098644.42</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Average estimated catches</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>41315.2589333333</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total catches (last 30 years)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22250748.19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total estimated catches (last 30 years)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1287880.28</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Average estimated catches (last 30 years)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>42929.34</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>t</t>
         </is>
       </c>
     </row>
@@ -425,7 +652,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -557,7 +784,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>3436</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -580,13 +807,13 @@
         </is>
       </c>
       <c r="F2">
-        <v>1950</v>
+        <v>1962</v>
       </c>
       <c r="G2">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="H2">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +822,47 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ALGÉRIE</t>
+          <t>EUROPEAN UNION</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>EU-France</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EU.FRA-FR</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BF59</t>
+          <t>BF54</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>MEDI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Traps</t>
+          <t>Bait boat</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -645,7 +872,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>EEZ</t>
+          <t>UNKN</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -662,7 +889,7 @@
         </is>
       </c>
       <c r="X2">
-        <v>100</v>
+        <v>965</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -672,16 +899,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>12628</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BON</t>
+          <t>BFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sarda sarda</t>
+          <t>Thunnus thynnus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -691,17 +918,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2-Tuna (small)</t>
+          <t>1-Tuna (major sp.)</t>
         </is>
       </c>
       <c r="F3">
-        <v>1950</v>
+        <v>1973</v>
       </c>
       <c r="G3">
-        <v>1950</v>
+        <v>1970</v>
       </c>
       <c r="H3">
-        <v>1950</v>
+        <v>1970</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -710,37 +937,37 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALGÉRIE</t>
+          <t>EUROPEAN UNION</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>EU-Sweden</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EU.SWE</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BIL95</t>
+          <t>BF54</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>MEDI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>All gears</t>
+          <t>Other surf.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -760,12 +987,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HSEA</t>
+          <t>UNKN</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>UNKN</t>
+          <t>RPT1</t>
         </is>
       </c>
       <c r="V3">
@@ -787,16 +1014,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>28623</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BON</t>
+          <t>YFT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sarda sarda</t>
+          <t>Thunnus albacares</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -806,46 +1033,46 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2-Tuna (small)</t>
+          <t>1-Tuna (major sp.)</t>
         </is>
       </c>
       <c r="F4">
-        <v>1950</v>
+        <v>1987</v>
       </c>
       <c r="G4">
-        <v>1950</v>
+        <v>1980</v>
       </c>
       <c r="H4">
-        <v>1950</v>
+        <v>1985</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NCO</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Non-contracting parties</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>A+M</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BIL96</t>
+          <t>YF09</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -855,17 +1082,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>All gears</t>
+          <t>Longline</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -880,7 +1107,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>RPT1</t>
         </is>
       </c>
       <c r="V4">
@@ -892,17 +1119,17 @@
         </is>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Reported</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>32802</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -925,32 +1152,32 @@
         </is>
       </c>
       <c r="F5">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="G5">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="H5">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>NCO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>Non-contracting parties</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -970,17 +1197,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bait boat</t>
+          <t>Other surf.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>UNCL</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -990,12 +1217,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>EEZ</t>
+          <t>UNKN</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>UNKN</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="V5">
@@ -1007,46 +1234,46 @@
         </is>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>48818</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BON</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sarda sarda</t>
+          <t>Istiophorus platypterus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Scombridae</t>
+          <t>Istiophoridae</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2-Tuna (small)</t>
+          <t>1-Tuna (major sp.)</t>
         </is>
       </c>
       <c r="F6">
-        <v>1950</v>
+        <v>1995</v>
       </c>
       <c r="G6">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="H6">
-        <v>1950</v>
+        <v>1995</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1055,47 +1282,47 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>VENEZUELA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BIL96</t>
+          <t>BIL94A</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>NW</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>All gears</t>
+          <t>Longline</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>UNCL</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1105,12 +1332,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HSEA</t>
+          <t>UNKN</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>UNKN</t>
+          <t>RPT1</t>
         </is>
       </c>
       <c r="V6">
@@ -1122,9 +1349,1734 @@
         </is>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>53436</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lamna nasus</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lamnidae</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4-Sharks (major)</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>1995</v>
+      </c>
+      <c r="G7">
+        <v>1990</v>
+      </c>
+      <c r="H7">
+        <v>1995</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EUROPEAN UNION</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EU-Denmark</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>EU.DNK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ANE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>BIL94B</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Other surf.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>UNCL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X7">
+        <v>86</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>53684</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Squaliformes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(unknown)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5-Sharks (other)</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>1987</v>
+      </c>
+      <c r="G8">
+        <v>1980</v>
+      </c>
+      <c r="H8">
+        <v>1985</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USA-US-Com</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A+M</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>BIL92</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V8">
+        <v>2.02</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X8">
+        <v>35.4</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>69063</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BLF</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Thunnus atlanticus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2-Tuna (small)</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>2006</v>
+      </c>
+      <c r="G9">
+        <v>2000</v>
+      </c>
+      <c r="H9">
+        <v>2005</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USA-US-Recr</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>BIL92</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X9">
+        <v>224.677</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>76448</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SPF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tetrapturus pfluegeri</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Istiophoridae</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>1985</v>
+      </c>
+      <c r="G10">
+        <v>1980</v>
+      </c>
+      <c r="H10">
+        <v>1985</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TRINIDAD &amp; TOBAGO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>TTO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>BIL93</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>WTRO</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Longline</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X10">
+        <v>0.001</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>78940</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BLT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Auxis rochei</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2-Tuna (small)</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>2009</v>
+      </c>
+      <c r="G11">
+        <v>2000</v>
+      </c>
+      <c r="H11">
+        <v>2005</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>EUROPEAN UNION</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>EU-France</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>EU.FRA-FR-MED</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BIL95</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MEDI</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GN</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>GILL</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X11">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>83244</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BON</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sarda sarda</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2-Tuna (small)</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>2010</v>
+      </c>
+      <c r="G12">
+        <v>2010</v>
+      </c>
+      <c r="H12">
+        <v>2010</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NORWAY</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>BIL94B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>UNCL</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X12">
+        <v>0.1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>109842</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SKJ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Katsuwonus pelamis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>1982</v>
+      </c>
+      <c r="G13">
+        <v>1980</v>
+      </c>
+      <c r="H13">
+        <v>1980</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CÔTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CIV-CI-ETRO</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SJ03</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>ETRO</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Purse seine</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UNKN</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X13">
+        <v>6357</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>118114</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thunnus alalunga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>2016</v>
+      </c>
+      <c r="G14">
+        <v>2010</v>
+      </c>
+      <c r="H14">
+        <v>2015</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MEXICO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ATN</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>AL32</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>GOFM</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Longline</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X14">
+        <v>2.194</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>122971</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BON</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sarda sarda</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2-Tuna (small)</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>2011</v>
+      </c>
+      <c r="G15">
+        <v>2010</v>
+      </c>
+      <c r="H15">
+        <v>2010</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MAURITANIA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BIL94B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>TRAW</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X15">
+        <v>9431.5</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>136159</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SKJ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Katsuwonus pelamis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>2018</v>
+      </c>
+      <c r="G16">
+        <v>2010</v>
+      </c>
+      <c r="H16">
+        <v>2015</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>EUROPEAN UNION</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>EU-France</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>EU.FRA-FR-ETRO</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SJ02</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>CVER</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Purse seine</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>COMB</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X16">
+        <v>0.499</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>138577</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SWO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Xiphias gladius</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Xiphiidae</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>2018</v>
+      </c>
+      <c r="G17">
+        <v>2010</v>
+      </c>
+      <c r="H17">
+        <v>2015</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MEXICO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ATN</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BIL91</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>GOFM</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Longline</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X17">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>141512</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SPZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sphyrna zygaena</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sphyrnidae</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5-Sharks (other)</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>2019</v>
+      </c>
+      <c r="G18">
+        <v>2010</v>
+      </c>
+      <c r="H18">
+        <v>2015</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CÔTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CIV-CI-Artisanal</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>A+M</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BIL97</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GN</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>GILL</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X18">
+        <v>1.861092</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>167615</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>THR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alopias spp</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Alopiidae</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5-Sharks (other)</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>2022</v>
+      </c>
+      <c r="G19">
+        <v>2020</v>
+      </c>
+      <c r="H19">
+        <v>2020</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>MEXICO</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A+M</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BIL91</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>GOFM</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>All gears</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="X19">
+        <v>0.015</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>173775</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thunnus alalunga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>2022</v>
+      </c>
+      <c r="G20">
+        <v>2020</v>
+      </c>
+      <c r="H20">
+        <v>2020</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USA-US-Com</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ATN</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>AL32</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NORT</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Longline</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>COMB</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V20">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="X20">
+        <v>58.689</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>183062</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Thunnus obesus</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>2023</v>
+      </c>
+      <c r="G21">
+        <v>2020</v>
+      </c>
+      <c r="H21">
+        <v>2020</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>SEN-SN-ETRO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A+M</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>BE02</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>CVER</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Purse seine</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>COMB</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>RPT1</t>
+        </is>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="X21">
+        <v>432.8</v>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Reported</t>
         </is>
@@ -1137,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1203,15 +3155,81 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sum of Qty_t</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YearC</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sum of Qty_t</t>
+          <t>SpeciesGrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ScieName</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>YearC</t>
+          <t>2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-Tuna (major sp.)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BUM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Makaira nigricans</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A+M</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6.4740000000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6.4740000000000002</t>
         </is>
       </c>
     </row>
@@ -1222,7 +3240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1272,17 +3290,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RPT1</t>
+          <t>RNAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reported Official</t>
+          <t>Reported (Nat. Rep.)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>As Reported by Nat. Off.</t>
+          <t>Data obtained from National Report</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1294,17 +3312,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RNAT</t>
+          <t>RSCR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reported (Nat. Rep.)</t>
+          <t>Reported (SCRS rev)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data obtained from National Report</t>
+          <t>Reported and with a posterior SCRS revision</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1316,17 +3334,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSCR</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reported (SCRS rev)</t>
+          <t>Rep. non-off (SCRS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reported and with a posterior SCRS revision</t>
+          <t>Un-official data accepted by SCRS (preliminary)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1338,22 +3356,352 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>CO2P</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rep. non-off (SCRS)</t>
+          <t>C. Over (avg 2p Yrs)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Un-official data accepted by SCRS (preliminary)</t>
+          <t>Carry over (average of previous 2(+) years)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CO3P</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C. Over (avg 3p Yrs)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Carry over (average of previous 3(+) years)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CO5P</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Over (avg 5p Yrs)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Carry over (average of previous 5(+) years)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CO7P</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C. Over (avg 7p Yrs)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Carry over (average of previous 7(+) years)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TROT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trade: other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Update based on other Trade source Comparison</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SECR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SCRS estimates (cr)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SCRS preliminary estimates (based on catch rates)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RCSP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Reclass.: Species</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Update based on Species reclassification</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RCAR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reclass.: Area</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Update based on Area reclassification</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RCGR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Reclass.: Gear</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Update based on Gear reclassification</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RCOT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Reclass.: Various</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Update based on Species/Area/Gear reclassification</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SPSP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Split: Species</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Update based on a Species breakdown</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SPAR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Split: Area</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Update based on an Area breakdown</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SPGR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Split: Gear</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Update based on an Gear breakdown</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Split: Various</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Update: Species/Area/Gear combination breakdown</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FAO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FAO stats</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FAO statistics (temporary)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ICES</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ICES stats</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ICES statistics (temporary)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estimated</t>
         </is>
       </c>
     </row>
@@ -1364,7 +3712,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1599,6 +3947,120 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BUM *5  WW=1.159*PW+1.834</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>linear (y=a+bx)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>1.834</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.159</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>used by JPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SAI *7  WW=0.793*PW+6.938</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>linear (y=a+bx)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>6.938</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.79300000000000004</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>used by JPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SPF *8  WW=1.157*PW+5.517</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>linear (y=a+bx)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>5.517</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.157</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>used by JPN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
